--- a/GATEWAY/A1#111#NIDEKTECHNOLOGIESSRLXX/nidek-technologies/nlife/210/report-checklist.xlsx
+++ b/GATEWAY/A1#111#NIDEKTECHNOLOGIESSRLXX/nidek-technologies/nlife/210/report-checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01 - RAD\02 - nLIFE\FBOV\FSE\PullRequest_20260304\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01 - RAD\02 - nLIFE\FBOV\FSE\PullRequest_20260305\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859A328F-3FB3-410B-8A55-411AFF7A420D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F649966-0984-4C18-B327-FD35A2069A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="522">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="273.60000000000002" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="343.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -4362,7 +4362,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="33">
         <v>4</v>
       </c>
@@ -4405,7 +4405,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>28</v>
       </c>
@@ -4448,7 +4448,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>29</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>30</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>31</v>
       </c>
@@ -5133,7 +5133,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>44</v>
       </c>
@@ -5162,13 +5162,27 @@
       <c r="L27" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="38"/>
-      <c r="P27" s="38"/>
-      <c r="Q27" s="38"/>
-      <c r="R27" s="38"/>
-      <c r="S27" s="38"/>
+      <c r="M27" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N27" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O27" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P27" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q27" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R27" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S27" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T27" s="38"/>
       <c r="U27" s="39"/>
       <c r="V27" s="40"/>
@@ -5176,7 +5190,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>45</v>
       </c>
@@ -5205,13 +5219,27 @@
       <c r="L28" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="38"/>
-      <c r="P28" s="38"/>
-      <c r="Q28" s="38"/>
-      <c r="R28" s="38"/>
-      <c r="S28" s="38"/>
+      <c r="M28" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N28" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O28" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P28" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q28" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R28" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S28" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T28" s="38"/>
       <c r="U28" s="39"/>
       <c r="V28" s="40"/>
@@ -5219,7 +5247,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>46</v>
       </c>
@@ -5248,13 +5276,27 @@
       <c r="L29" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
-      <c r="S29" s="38"/>
+      <c r="M29" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N29" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O29" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P29" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q29" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R29" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S29" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T29" s="38"/>
       <c r="U29" s="39"/>
       <c r="V29" s="40"/>
@@ -5262,7 +5304,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>47</v>
       </c>
@@ -5291,13 +5333,27 @@
       <c r="L30" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="38"/>
-      <c r="P30" s="38"/>
-      <c r="Q30" s="38"/>
-      <c r="R30" s="38"/>
-      <c r="S30" s="38"/>
+      <c r="M30" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N30" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O30" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P30" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q30" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R30" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S30" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T30" s="38"/>
       <c r="U30" s="39"/>
       <c r="V30" s="40"/>
@@ -5326,14 +5382,10 @@
       <c r="H31" s="37"/>
       <c r="I31" s="42"/>
       <c r="J31" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="K31" s="38" t="s">
-        <v>491</v>
-      </c>
-      <c r="L31" s="38" t="s">
-        <v>521</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
       <c r="M31" s="47" t="s">
         <v>67</v>
       </c>
@@ -5362,7 +5414,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>49</v>
       </c>
@@ -5391,13 +5443,27 @@
       <c r="L32" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="38"/>
-      <c r="P32" s="38"/>
-      <c r="Q32" s="38"/>
-      <c r="R32" s="38"/>
-      <c r="S32" s="38"/>
+      <c r="M32" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N32" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O32" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P32" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q32" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R32" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S32" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T32" s="38"/>
       <c r="U32" s="39"/>
       <c r="V32" s="40"/>
@@ -5405,7 +5471,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>50</v>
       </c>
@@ -5434,13 +5500,27 @@
       <c r="L33" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="38"/>
-      <c r="P33" s="38"/>
-      <c r="Q33" s="38"/>
-      <c r="R33" s="38"/>
-      <c r="S33" s="38"/>
+      <c r="M33" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N33" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O33" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P33" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q33" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R33" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S33" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T33" s="38"/>
       <c r="U33" s="39"/>
       <c r="V33" s="40"/>
@@ -5448,7 +5528,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>51</v>
       </c>
@@ -5477,13 +5557,27 @@
       <c r="L34" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="38"/>
-      <c r="P34" s="38"/>
-      <c r="Q34" s="38"/>
-      <c r="R34" s="38"/>
-      <c r="S34" s="38"/>
+      <c r="M34" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N34" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O34" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P34" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q34" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R34" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S34" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T34" s="38"/>
       <c r="U34" s="39"/>
       <c r="V34" s="40"/>
@@ -10744,7 +10838,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="150" spans="1:23" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:23" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A150" s="35">
         <v>419</v>
       </c>
@@ -10787,7 +10881,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="151" spans="1:23" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A151" s="35">
         <v>423</v>
       </c>
@@ -10830,7 +10924,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="152" spans="1:23" ht="144" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:23" ht="144" x14ac:dyDescent="0.3">
       <c r="A152" s="35">
         <v>424</v>
       </c>
@@ -10873,7 +10967,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="153" spans="1:23" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A153" s="35">
         <v>425</v>
       </c>
@@ -10902,13 +10996,27 @@
       <c r="L153" s="38" t="s">
         <v>521</v>
       </c>
-      <c r="M153" s="38"/>
-      <c r="N153" s="38"/>
-      <c r="O153" s="38"/>
-      <c r="P153" s="38"/>
-      <c r="Q153" s="38"/>
-      <c r="R153" s="38"/>
-      <c r="S153" s="38"/>
+      <c r="M153" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="N153" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="O153" s="48" t="s">
+        <v>94</v>
+      </c>
+      <c r="P153" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q153" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="R153" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="S153" s="49" t="s">
+        <v>70</v>
+      </c>
       <c r="T153" s="38"/>
       <c r="U153" s="39"/>
       <c r="V153" s="40"/>
@@ -10916,7 +11024,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="154" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A154" s="35">
         <v>432</v>
       </c>
@@ -10959,7 +11067,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="155" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A155" s="35">
         <v>433</v>
       </c>
@@ -11002,7 +11110,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="156" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A156" s="35">
         <v>434</v>
       </c>
@@ -11045,7 +11153,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="157" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A157" s="35">
         <v>435</v>
       </c>
@@ -11088,7 +11196,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="158" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A158" s="35">
         <v>437</v>
       </c>
@@ -11131,7 +11239,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="159" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A159" s="35">
         <v>438</v>
       </c>
@@ -11174,7 +11282,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="160" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A160" s="35">
         <v>440</v>
       </c>
@@ -11217,7 +11325,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="161" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A161" s="35">
         <v>441</v>
       </c>
@@ -11260,7 +11368,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="162" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A162" s="35">
         <v>442</v>
       </c>
@@ -11303,7 +11411,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="163" spans="1:23" ht="115.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:23" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A163" s="35">
         <v>443</v>
       </c>
@@ -16715,7 +16823,7 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>P32:R193 M32:N193 P10:R30 M10:N30 J10:J193</xm:sqref>
+          <xm:sqref>M154:N193 J10:J193 M35:N152 P154:R193 P35:R152 M10:N26 P10:R26</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>

--- a/GATEWAY/A1#111#NIDEKTECHNOLOGIESSRLXX/nidek-technologies/nlife/210/report-checklist.xlsx
+++ b/GATEWAY/A1#111#NIDEKTECHNOLOGIESSRLXX/nidek-technologies/nlife/210/report-checklist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01 - RAD\02 - nLIFE\FBOV\FSE\PullRequest_20260305\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RAD\08 - Lab\FSE\validazione_accreditamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F649966-0984-4C18-B327-FD35A2069A99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97E6315D-C80E-45D7-944E-EC9AC95ACAA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -75,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -385,13 +385,13 @@
     <t>VALIDAZIONE_TOKEN_JWT_RSA_KO</t>
   </si>
   <si>
-    <t>2026-03-11</t>
-  </si>
-  <si>
-    <t>2026-03-11T10:19:52Z</t>
-  </si>
-  <si>
-    <t>d909b8f040d12f072b5c0d6e2b9f57bc</t>
+    <t>2026-03-18</t>
+  </si>
+  <si>
+    <t>2026-03-18T08:35:32Z</t>
+  </si>
+  <si>
+    <t>87c63abd2abeda85a49e30647271c110</t>
   </si>
   <si>
     <t>UNKNOWN_WORKFLOW_ID</t>
@@ -481,7 +481,7 @@
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_RSA_KO</t>
   </si>
   <si>
-    <t>043991e0520ad2ceac758dba32654fc5</t>
+    <t>cea49fa606fa4efdc89ebaa3b248d157</t>
   </si>
   <si>
     <t>VALIDAZIONE_TOKEN_JWT_CAMPO_CERT_VAC_KO</t>
@@ -1099,10 +1099,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>aadeeb83c60c19b54941b07086f35867</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7a2ef2e472^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:33Z</t>
+  </si>
+  <si>
+    <t>5e6da4ce56a520275da773b39bf2adef</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.784c5b04e4^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT8_KO</t>
@@ -1112,13 +1115,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:53Z</t>
-  </si>
-  <si>
-    <t>5d796329c4ffe017908d4cf4e9bf1844</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.71af2aa68f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>6bf48917b26d118831b694823898de42</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.617b6c9219^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT9_KO</t>
@@ -1128,10 +1128,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>f2add514eccb3548a5935429ce7a1502</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.de07123bb6^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:34Z</t>
+  </si>
+  <si>
+    <t>b918070b612379f7969350adb009516b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.05a94cf447^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT10_KO</t>
@@ -1141,13 +1144,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:54Z</t>
-  </si>
-  <si>
-    <t>5629108bbf6ab24d33d57787b322752d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.1b47e5e799^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>5b2ee03e4e1d99423c48908c6aa183f1</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.568576b9ba^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT13_KO</t>
@@ -1157,10 +1157,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>b08b94ae4ba731e9bc37d4f74ade2bac</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.aad8076639^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>62b7024b81622400ce0e05715f4b1597</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.377c78d65d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT14_KO</t>
@@ -1170,10 +1170,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2f28f1f38743fa97e17f309f2e5639bb</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.7f4a6e825b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:35Z</t>
+  </si>
+  <si>
+    <t>436ca9f982655214524edd7adf3f0294</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.ad34d22c39^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT15_KO</t>
@@ -1183,10 +1186,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>ea2b02cd44311854ae4a123dc46cc4d1</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.cd1a5492a5^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>fbb1e8c22a87b2b14f4d57da580c6e38</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.791fa5e793^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT16_KO</t>
@@ -1196,13 +1199,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:55Z</t>
-  </si>
-  <si>
-    <t>6dd64400ad92daed3a8b2d766b3699e5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3e1067532d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>dda53c7f6f137a029cf55c382a21a339</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.22527b2c89^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT17_KO</t>
@@ -1212,10 +1212,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>c3e9a602f76492e80f21ac0616c9396e</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3b2c41c5d9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:36Z</t>
+  </si>
+  <si>
+    <t>f0ee05b83c3ed505a8ca1e51137c25ee</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.14395a374f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT18_KO</t>
@@ -1225,10 +1228,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>72c9264f6ed259bd3a80622b38a6b554</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.af4017a535^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>af6a7c137c9533eb42323c0fbe27eb46</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.1c9ddc4512^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT19_KO</t>
@@ -1238,13 +1241,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:56Z</t>
-  </si>
-  <si>
-    <t>75a678ca6bd90f130151a833edd73b88</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.e09da79e76^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>5f07be35a72ca943e9f5d0ef1cc18da5</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.0fcc69cb03^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT20_KO</t>
@@ -1254,10 +1254,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>c76bd0f83530bcfba35388ceebd7da8d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.05aad5780d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:37Z</t>
+  </si>
+  <si>
+    <t>236bb7d7a81498f035d202266666dde3</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.ab5602a358^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT21_KO</t>
@@ -1267,10 +1270,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>4aaeddc0f56acd19671571da9eb5ad26</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.007ee582de^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>7cf6ed05c21d56865809d911a07520b1</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.dcedc26442^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT22_KO</t>
@@ -1280,13 +1283,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:57Z</t>
-  </si>
-  <si>
-    <t>5c10c94ce67db075ac16d131cc6f4e48</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.6219fe1992^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>cda024c1f5556066dcd7637210c25341</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.56adf63115^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT23_KO</t>
@@ -1296,10 +1296,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>3ce2d4a79e96a181544b1a35642d64aa</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.0a1e43937a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:38Z</t>
+  </si>
+  <si>
+    <t>341cd207f56ab8c7e0fe954a302bee2c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.bc01e07fcc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT6_KO</t>
@@ -1433,15 +1436,6 @@
 Il Documento CDA2 Anatomia Patologica dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 1" riportata nei documenti "casi di test RAP" e "CDA2_Referto_di_Anatomia_Patologica_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:20:00Z</t>
-  </si>
-  <si>
-    <t>cd11a61e622e604aceffb4cab85596d5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.0e508305c2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_RAP_CT2</t>
   </si>
   <si>
@@ -1450,15 +1444,6 @@
 </t>
   </si>
   <si>
-    <t>2026-03-11T10:20:01Z</t>
-  </si>
-  <si>
-    <t>cc0db2b0e62eead2a833cc3f3cb60ef2</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.21a88e05bc^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_RAP_CT3</t>
   </si>
   <si>
@@ -1557,10 +1542,10 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>4ff51850c8ae691e1665947d06e0fc40</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.093d7b71ed^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>159fb29437d61326c6e1d5c0cf5df5ee</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.6d6a1c49cf^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RSA_CT25</t>
@@ -1570,13 +1555,10 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:58Z</t>
-  </si>
-  <si>
-    <t>0c159b4d1adf4b7dcf707945b0f46091</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.acc7cbd1a3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>bede4cd57ab14f779f5df920a25bf934</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.9359e2eb13^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_LDO_CT17</t>
@@ -1584,15 +1566,6 @@
   <si>
     <t xml:space="preserve">Viene richiamato il servizio di validazione "https://&lt;HOST&gt;:&lt;PORT&gt;/v&lt;major&gt;/documents/validation" al fine di una futura pubblicazione con esito positivo (status code 201), secondo quanto descritto in https://github.com/ministero-salute/it-fse-support/tree/main/doc/integrazione-gateway
 Il Documento CDA2 Lettera Dimissione Ospedaliera dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 17" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
-  </si>
-  <si>
-    <t>2026-03-11T10:20:02Z</t>
-  </si>
-  <si>
-    <t>d0ac48c8ed4028c5ebea184985d7e5ea</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.b0f3ffcf25ce2aafc7dc901e2febc51f43837f4ca0fe3b6d1b02194e9047b6db.b23fa035c1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_LDO_CT18</t>
@@ -1610,15 +1583,6 @@
 </t>
   </si>
   <si>
-    <t>2026-03-11T10:20:03Z</t>
-  </si>
-  <si>
-    <t>fd7e128e7e4bc2fda4578ffa3c7b63e7</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.03d7b99f01^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_VPS_CT30</t>
   </si>
   <si>
@@ -1626,12 +1590,6 @@
 Il Documento CDA2 Verbale di Pronto Soccorso dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 30" riportata nei documenti "casi di test VPS" e "CDA2_Verbale_Pronto_Soccorso_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>073c9ee35154b6dedc9902c90b1ed15b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.46a41df0ab0514f11c0811056832c3225e06c8e11824f27c7e5517ca5cfc57fe.b139f5655c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_VPS_CT31</t>
   </si>
   <si>
@@ -1646,12 +1604,6 @@
 Il Documento CDA2 Scheda Singola Vaccinazione dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 4" riportata nei documenti "casi di test SING_VACC" e "CDA2_Scheda_Singola Vaccinazione_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>f9e6754b83001a310ed6650e290a4335</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.46a41df0ab0514f11c0811056832c3225e06c8e11824f27c7e5517ca5cfc57fe.42bf830387^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_SING_VAC_CT20</t>
   </si>
   <si>
@@ -1659,12 +1611,6 @@
 Il Documento CDA2 Scheda Singola Vaccinazione dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 20" riportata nei documenti "casi di test SING_VACC" e "CDA2_Scheda_Singola Vaccinazione_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>7d2749c1d69f474cd3cd3b163b23fcb6</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.46a41df0ab0514f11c0811056832c3225e06c8e11824f27c7e5517ca5cfc57fe.c0e545a3ef^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_CERT_VAC_CT18</t>
   </si>
   <si>
@@ -1672,15 +1618,6 @@
 Il Documento CDA2 Certificato Vaccinale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 18" riportata nei documenti "casi di test CERT_VACC" e "CDA2_Certificato Vaccinale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:20:04Z</t>
-  </si>
-  <si>
-    <t>659b7a467b8dd71586f6be3bfe4e3fd3</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.46a41df0ab0514f11c0811056832c3225e06c8e11824f27c7e5517ca5cfc57fe.585a4936df^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_CERT_VAC_CT19</t>
   </si>
   <si>
@@ -1695,12 +1632,6 @@
 Il Documento CDA2 Anatomia Patologica dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RAP" e "CDA2_Referto_di_Anatomia_Patologica_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>d66573aa68f67301a356e52ea628dd8c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.97bb3fc5bee3032679f4f07419e04af6375baafa17024527a98ede920c6812ed.c05930fc44^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_RSA_CT26_KO</t>
   </si>
   <si>
@@ -1708,10 +1639,13 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>69622ba8ee2356b869af6e8c83c19f78</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.3a2e0ba3df^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-03-18T08:35:39Z</t>
+  </si>
+  <si>
+    <t>2149b5e215a911b60e97452ba85b4cda</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.d183aa673b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_RAD_CT24_KO</t>
@@ -1763,10 +1697,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>d4460342c6bb3fd0735dad574ccda694</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.585c269aa3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>b701bba209a5d14801cc5a576d1a5d4e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.43db55d08a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT22_KO</t>
@@ -1790,12 +1724,6 @@
 Il Documento CDA2 Referto Radiologia dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RAD" e "CDA2_Referto_di_Radiologia_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2c60513430edd324fbe8ddb7d56a949f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.8fe46b71d98546dc779f4a7f4859b056b254bbe56b59baa550333b2c46441c87.d5d6ec3c44^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>VALIDAZIONE_CDA2_RAD_CT26</t>
   </si>
   <si>
@@ -1824,13 +1752,10 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
   </si>
   <si>
-    <t>2026-03-11T10:19:59Z</t>
-  </si>
-  <si>
-    <t>bdbaf964f7dd915b54720cb19b9bab3d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.bcb45ddf63^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>5d9f49778c8b59d424b883c694175a2f</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.780b271a01^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
   <si>
     <t>VALIDAZIONE_CDA2_PSS_CT23</t>
@@ -2929,10 +2854,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="130.109375" customWidth="1"/>
-    <col min="2" max="26" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="130.140625" customWidth="1"/>
+    <col min="2" max="26" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2940,27 +2865,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="86.4">
+    <row r="2" ht="90">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="28.8">
+    <row r="3" ht="30">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="72">
+    <row r="4" ht="90">
       <c r="A4" s="46" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" ht="343.2" customHeight="1">
+    <row r="5" ht="343.15" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" ht="86.4">
+    <row r="6" ht="90">
       <c r="A6" s="17" t="s">
         <v>5</v>
       </c>
@@ -2978,7 +2903,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" ht="28.8">
+    <row r="10" ht="45">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -3004,11 +2929,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
-    <col min="2" max="2" width="194.109375" customWidth="1"/>
-    <col min="3" max="6" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="2" width="194.140625" customWidth="1"/>
+    <col min="3" max="6" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -4068,23 +3993,22 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:W745"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" customWidth="1"/>
-    <col min="2" max="2" width="46.88671875" customWidth="1"/>
-    <col min="3" max="3" width="20.109375" customWidth="1"/>
-    <col min="4" max="4" width="63.88671875" customWidth="1"/>
-    <col min="5" max="5" width="104.88671875" customWidth="1"/>
-    <col min="6" max="9" width="33.109375" customWidth="1"/>
-    <col min="10" max="10" width="27.109375" customWidth="1"/>
-    <col min="11" max="18" width="36.44140625" customWidth="1"/>
-    <col min="19" max="19" width="27.109375" customWidth="1"/>
-    <col min="20" max="20" width="33.109375" customWidth="1"/>
-    <col min="21" max="21" width="36.44140625" customWidth="1"/>
-    <col min="22" max="23" width="31.88671875" customWidth="1"/>
-    <col min="27" max="27" bestFit="1" width="30.88671875" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="63.85546875" customWidth="1"/>
+    <col min="5" max="5" width="104.85546875" customWidth="1"/>
+    <col min="6" max="9" width="33.140625" customWidth="1"/>
+    <col min="10" max="10" width="27.140625" customWidth="1"/>
+    <col min="11" max="18" width="36.42578125" customWidth="1"/>
+    <col min="19" max="19" width="27.140625" customWidth="1"/>
+    <col min="20" max="20" width="33.140625" customWidth="1"/>
+    <col min="21" max="21" width="36.42578125" customWidth="1"/>
+    <col min="22" max="23" width="31.85546875" customWidth="1"/>
+    <col min="27" max="27" bestFit="1" width="30.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4108,7 +4032,7 @@
       <c r="V1" s="2"/>
       <c r="W1" s="9"/>
     </row>
-    <row r="2" ht="18">
+    <row r="2" ht="18.75">
       <c r="A2" s="52" t="s">
         <v>18</v>
       </c>
@@ -4136,7 +4060,7 @@
       <c r="V2" s="2"/>
       <c r="W2" s="9"/>
     </row>
-    <row r="3" ht="15.6">
+    <row r="3" ht="15.75">
       <c r="A3" s="56" t="s">
         <v>20</v>
       </c>
@@ -4164,7 +4088,7 @@
       <c r="V3" s="2"/>
       <c r="W3" s="9"/>
     </row>
-    <row r="4" ht="15.6">
+    <row r="4" ht="15.75">
       <c r="A4" s="58"/>
       <c r="B4" s="59"/>
       <c r="C4" s="62" t="s">
@@ -4191,7 +4115,7 @@
       <c r="V4" s="2"/>
       <c r="W4" s="9"/>
     </row>
-    <row r="5" ht="15.6">
+    <row r="5" ht="15.75">
       <c r="A5" s="60"/>
       <c r="B5" s="61"/>
       <c r="C5" s="62" t="s">
@@ -4283,7 +4207,7 @@
       <c r="V8" s="2"/>
       <c r="W8" s="9"/>
     </row>
-    <row r="9" ht="108" s="18" customFormat="1">
+    <row r="9" ht="131.25" s="18" customFormat="1">
       <c r="A9" s="19" t="s">
         <v>24</v>
       </c>
@@ -4354,7 +4278,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="10" ht="129.6">
+    <row r="10" ht="150">
       <c r="A10" s="33">
         <v>4</v>
       </c>
@@ -4397,7 +4321,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" ht="144">
+    <row r="11" ht="150">
       <c r="A11" s="35">
         <v>28</v>
       </c>
@@ -4440,7 +4364,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" ht="144">
+    <row r="12" ht="150">
       <c r="A12" s="35">
         <v>29</v>
       </c>
@@ -4483,7 +4407,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="13" ht="144">
+    <row r="13" ht="150">
       <c r="A13" s="35">
         <v>30</v>
       </c>
@@ -4526,7 +4450,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" ht="144">
+    <row r="14" ht="150">
       <c r="A14" s="35">
         <v>31</v>
       </c>
@@ -4569,7 +4493,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="15" ht="144">
+    <row r="15" ht="150">
       <c r="A15" s="35">
         <v>32</v>
       </c>
@@ -4632,7 +4556,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" ht="144">
+    <row r="16" ht="150">
       <c r="A16" s="35">
         <v>33</v>
       </c>
@@ -4675,7 +4599,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="17" ht="144">
+    <row r="17" ht="150">
       <c r="A17" s="35">
         <v>34</v>
       </c>
@@ -4718,7 +4642,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" ht="144">
+    <row r="18" ht="150">
       <c r="A18" s="35">
         <v>35</v>
       </c>
@@ -4761,7 +4685,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" ht="144">
+    <row r="19" ht="165">
       <c r="A19" s="35">
         <v>36</v>
       </c>
@@ -4804,7 +4728,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" ht="144">
+    <row r="20" ht="165">
       <c r="A20" s="35">
         <v>37</v>
       </c>
@@ -4847,7 +4771,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" ht="144">
+    <row r="21" ht="165">
       <c r="A21" s="35">
         <v>38</v>
       </c>
@@ -4890,7 +4814,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" ht="144">
+    <row r="22" ht="165">
       <c r="A22" s="35">
         <v>39</v>
       </c>
@@ -4933,7 +4857,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" ht="144">
+    <row r="23" ht="165">
       <c r="A23" s="35">
         <v>40</v>
       </c>
@@ -4996,7 +4920,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" ht="144">
+    <row r="24" ht="165">
       <c r="A24" s="35">
         <v>41</v>
       </c>
@@ -5039,7 +4963,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" ht="144">
+    <row r="25" ht="165">
       <c r="A25" s="35">
         <v>42</v>
       </c>
@@ -5082,7 +5006,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" ht="144">
+    <row r="26" ht="165">
       <c r="A26" s="35">
         <v>43</v>
       </c>
@@ -5125,7 +5049,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" ht="115.2">
+    <row r="27" ht="150">
       <c r="A27" s="35">
         <v>44</v>
       </c>
@@ -5182,7 +5106,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" ht="115.2">
+    <row r="28" ht="150">
       <c r="A28" s="35">
         <v>45</v>
       </c>
@@ -5239,7 +5163,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" ht="115.2">
+    <row r="29" ht="150">
       <c r="A29" s="35">
         <v>46</v>
       </c>
@@ -5296,7 +5220,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" ht="115.2">
+    <row r="30" ht="150">
       <c r="A30" s="35">
         <v>47</v>
       </c>
@@ -5353,7 +5277,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="31" ht="115.2">
+    <row r="31" ht="150">
       <c r="A31" s="35">
         <v>48</v>
       </c>
@@ -5406,7 +5330,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" ht="115.2">
+    <row r="32" ht="150">
       <c r="A32" s="35">
         <v>49</v>
       </c>
@@ -5463,7 +5387,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" ht="115.2">
+    <row r="33" ht="150">
       <c r="A33" s="35">
         <v>50</v>
       </c>
@@ -5520,7 +5444,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" ht="115.2">
+    <row r="34" ht="150">
       <c r="A34" s="35">
         <v>51</v>
       </c>
@@ -5577,7 +5501,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" ht="115.2">
+    <row r="35" ht="120">
       <c r="A35" s="35">
         <v>53</v>
       </c>
@@ -5620,7 +5544,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="36" ht="115.2">
+    <row r="36" ht="120">
       <c r="A36" s="35">
         <v>55</v>
       </c>
@@ -5663,7 +5587,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" ht="115.2">
+    <row r="37" ht="120">
       <c r="A37" s="35">
         <v>56</v>
       </c>
@@ -5706,7 +5630,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="38" ht="115.2">
+    <row r="38" ht="120">
       <c r="A38" s="35">
         <v>57</v>
       </c>
@@ -5749,7 +5673,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="39" ht="115.2">
+    <row r="39" ht="120">
       <c r="A39" s="35">
         <v>59</v>
       </c>
@@ -5792,7 +5716,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="40" ht="115.2">
+    <row r="40" ht="120">
       <c r="A40" s="35">
         <v>60</v>
       </c>
@@ -5835,7 +5759,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="41" ht="115.2">
+    <row r="41" ht="120">
       <c r="A41" s="35">
         <v>61</v>
       </c>
@@ -5878,7 +5802,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="42" ht="115.2">
+    <row r="42" ht="120">
       <c r="A42" s="35">
         <v>62</v>
       </c>
@@ -5921,7 +5845,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="43" ht="100.8">
+    <row r="43" ht="105">
       <c r="A43" s="35">
         <v>64</v>
       </c>
@@ -5964,7 +5888,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="44" ht="100.8">
+    <row r="44" ht="105">
       <c r="A44" s="35">
         <v>66</v>
       </c>
@@ -6007,7 +5931,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" ht="100.8">
+    <row r="45" ht="105">
       <c r="A45" s="35">
         <v>67</v>
       </c>
@@ -6050,7 +5974,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="46" ht="100.8">
+    <row r="46" ht="105">
       <c r="A46" s="35">
         <v>68</v>
       </c>
@@ -6093,7 +6017,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="47" ht="100.8">
+    <row r="47" ht="105">
       <c r="A47" s="35">
         <v>69</v>
       </c>
@@ -6136,7 +6060,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="48" ht="100.8">
+    <row r="48" ht="105">
       <c r="A48" s="35">
         <v>70</v>
       </c>
@@ -6179,7 +6103,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" ht="100.8">
+    <row r="49" ht="105">
       <c r="A49" s="35">
         <v>71</v>
       </c>
@@ -6222,7 +6146,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="50" ht="100.8">
+    <row r="50" ht="105">
       <c r="A50" s="35">
         <v>72</v>
       </c>
@@ -6265,7 +6189,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" ht="100.8">
+    <row r="51" ht="105">
       <c r="A51" s="35">
         <v>73</v>
       </c>
@@ -6308,7 +6232,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="52" ht="100.8">
+    <row r="52" ht="105">
       <c r="A52" s="35">
         <v>74</v>
       </c>
@@ -6351,7 +6275,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="53" ht="100.8">
+    <row r="53" ht="105">
       <c r="A53" s="35">
         <v>76</v>
       </c>
@@ -6394,7 +6318,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" ht="100.8">
+    <row r="54" ht="105">
       <c r="A54" s="35">
         <v>78</v>
       </c>
@@ -6437,7 +6361,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" ht="100.8">
+    <row r="55" ht="105">
       <c r="A55" s="35">
         <v>79</v>
       </c>
@@ -6480,7 +6404,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" ht="100.8">
+    <row r="56" ht="105">
       <c r="A56" s="35">
         <v>80</v>
       </c>
@@ -6523,7 +6447,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" ht="100.8">
+    <row r="57" ht="105">
       <c r="A57" s="35">
         <v>81</v>
       </c>
@@ -6566,7 +6490,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="58" ht="100.8">
+    <row r="58" ht="105">
       <c r="A58" s="35">
         <v>83</v>
       </c>
@@ -6609,7 +6533,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" ht="100.8">
+    <row r="59" ht="105">
       <c r="A59" s="35">
         <v>84</v>
       </c>
@@ -6652,7 +6576,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" ht="100.8">
+    <row r="60" ht="105">
       <c r="A60" s="35">
         <v>85</v>
       </c>
@@ -6695,7 +6619,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="61" ht="100.8">
+    <row r="61" ht="105">
       <c r="A61" s="35">
         <v>86</v>
       </c>
@@ -6738,7 +6662,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" ht="115.2">
+    <row r="62" ht="120">
       <c r="A62" s="35">
         <v>87</v>
       </c>
@@ -6781,7 +6705,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" ht="100.8">
+    <row r="63" ht="105">
       <c r="A63" s="35">
         <v>88</v>
       </c>
@@ -6824,7 +6748,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" ht="100.8">
+    <row r="64" ht="105">
       <c r="A64" s="35">
         <v>89</v>
       </c>
@@ -6867,7 +6791,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" ht="100.8">
+    <row r="65" ht="105">
       <c r="A65" s="35">
         <v>90</v>
       </c>
@@ -6910,7 +6834,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" ht="100.8">
+    <row r="66" ht="105">
       <c r="A66" s="35">
         <v>91</v>
       </c>
@@ -6953,7 +6877,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" ht="100.8">
+    <row r="67" ht="105">
       <c r="A67" s="35">
         <v>92</v>
       </c>
@@ -6996,7 +6920,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="68" ht="100.8">
+    <row r="68" ht="105">
       <c r="A68" s="35">
         <v>93</v>
       </c>
@@ -7039,7 +6963,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" ht="115.2">
+    <row r="69" ht="120">
       <c r="A69" s="35">
         <v>95</v>
       </c>
@@ -7082,7 +7006,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" ht="100.8">
+    <row r="70" ht="105">
       <c r="A70" s="35">
         <v>97</v>
       </c>
@@ -7125,7 +7049,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="71" ht="115.2">
+    <row r="71" ht="120">
       <c r="A71" s="35">
         <v>98</v>
       </c>
@@ -7168,7 +7092,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="72" ht="115.2">
+    <row r="72" ht="120">
       <c r="A72" s="35">
         <v>99</v>
       </c>
@@ -7211,7 +7135,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="73" ht="100.8">
+    <row r="73" ht="105">
       <c r="A73" s="35">
         <v>100</v>
       </c>
@@ -7254,7 +7178,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="74" ht="100.8">
+    <row r="74" ht="105">
       <c r="A74" s="35">
         <v>101</v>
       </c>
@@ -7297,7 +7221,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="75" ht="115.2">
+    <row r="75" ht="120">
       <c r="A75" s="35">
         <v>102</v>
       </c>
@@ -7340,7 +7264,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="76" ht="115.2">
+    <row r="76" ht="120">
       <c r="A76" s="35">
         <v>103</v>
       </c>
@@ -7383,7 +7307,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" ht="100.8">
+    <row r="77" ht="105">
       <c r="A77" s="35">
         <v>104</v>
       </c>
@@ -7426,7 +7350,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" ht="115.2">
+    <row r="78" ht="120">
       <c r="A78" s="35">
         <v>105</v>
       </c>
@@ -7469,7 +7393,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" ht="115.2">
+    <row r="79" ht="120">
       <c r="A79" s="35">
         <v>106</v>
       </c>
@@ -7512,7 +7436,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="80" ht="100.8">
+    <row r="80" ht="105">
       <c r="A80" s="35">
         <v>108</v>
       </c>
@@ -7555,7 +7479,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="81" ht="100.8">
+    <row r="81" ht="105">
       <c r="A81" s="35">
         <v>110</v>
       </c>
@@ -7598,7 +7522,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="82" ht="100.8">
+    <row r="82" ht="105">
       <c r="A82" s="35">
         <v>111</v>
       </c>
@@ -7641,7 +7565,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="83" ht="100.8">
+    <row r="83" ht="105">
       <c r="A83" s="35">
         <v>112</v>
       </c>
@@ -7684,7 +7608,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" ht="100.8">
+    <row r="84" ht="105">
       <c r="A84" s="35">
         <v>113</v>
       </c>
@@ -7727,7 +7651,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" ht="100.8">
+    <row r="85" ht="105">
       <c r="A85" s="35">
         <v>114</v>
       </c>
@@ -7770,7 +7694,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" ht="100.8">
+    <row r="86" ht="105">
       <c r="A86" s="35">
         <v>115</v>
       </c>
@@ -7813,7 +7737,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="87" ht="100.8">
+    <row r="87" ht="105">
       <c r="A87" s="35">
         <v>116</v>
       </c>
@@ -7856,7 +7780,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="88" ht="100.8">
+    <row r="88" ht="105">
       <c r="A88" s="35">
         <v>117</v>
       </c>
@@ -7899,7 +7823,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" ht="100.8">
+    <row r="89" ht="105">
       <c r="A89" s="35">
         <v>118</v>
       </c>
@@ -7942,7 +7866,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" ht="100.8">
+    <row r="90" ht="105">
       <c r="A90" s="35">
         <v>119</v>
       </c>
@@ -7985,7 +7909,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" ht="100.8">
+    <row r="91" ht="105">
       <c r="A91" s="35">
         <v>120</v>
       </c>
@@ -8028,7 +7952,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" ht="100.8">
+    <row r="92" ht="105">
       <c r="A92" s="35">
         <v>121</v>
       </c>
@@ -8071,7 +7995,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" ht="100.8">
+    <row r="93" ht="105">
       <c r="A93" s="35">
         <v>123</v>
       </c>
@@ -8114,7 +8038,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="94" ht="100.8">
+    <row r="94" ht="105">
       <c r="A94" s="35">
         <v>125</v>
       </c>
@@ -8157,7 +8081,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="95" ht="100.8">
+    <row r="95" ht="105">
       <c r="A95" s="35">
         <v>126</v>
       </c>
@@ -8200,7 +8124,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" ht="100.8">
+    <row r="96" ht="120">
       <c r="A96" s="35">
         <v>127</v>
       </c>
@@ -8243,7 +8167,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="97" ht="100.8">
+    <row r="97" ht="120">
       <c r="A97" s="35">
         <v>128</v>
       </c>
@@ -8286,7 +8210,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" ht="100.8">
+    <row r="98" ht="120">
       <c r="A98" s="35">
         <v>129</v>
       </c>
@@ -8329,7 +8253,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" ht="100.8">
+    <row r="99" ht="120">
       <c r="A99" s="35">
         <v>130</v>
       </c>
@@ -8372,7 +8296,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="100" ht="100.8">
+    <row r="100" ht="120">
       <c r="A100" s="35">
         <v>131</v>
       </c>
@@ -8415,7 +8339,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" ht="100.8">
+    <row r="101" ht="120">
       <c r="A101" s="35">
         <v>132</v>
       </c>
@@ -8458,7 +8382,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" ht="100.8">
+    <row r="102" ht="120">
       <c r="A102" s="35">
         <v>133</v>
       </c>
@@ -8501,7 +8425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" ht="100.8">
+    <row r="103" ht="120">
       <c r="A103" s="35">
         <v>134</v>
       </c>
@@ -8544,7 +8468,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" ht="100.8">
+    <row r="104" ht="120">
       <c r="A104" s="35">
         <v>135</v>
       </c>
@@ -8587,7 +8511,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="105" ht="100.8">
+    <row r="105" ht="120">
       <c r="A105" s="35">
         <v>136</v>
       </c>
@@ -8630,7 +8554,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" ht="100.8">
+    <row r="106" ht="120">
       <c r="A106" s="35">
         <v>137</v>
       </c>
@@ -8673,7 +8597,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="107" ht="100.8">
+    <row r="107" ht="120">
       <c r="A107" s="35">
         <v>138</v>
       </c>
@@ -8716,7 +8640,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="108" ht="100.8">
+    <row r="108" ht="120">
       <c r="A108" s="35">
         <v>139</v>
       </c>
@@ -8759,7 +8683,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="109" ht="100.8">
+    <row r="109" ht="120">
       <c r="A109" s="35">
         <v>140</v>
       </c>
@@ -8802,7 +8726,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" ht="100.8">
+    <row r="110" ht="120">
       <c r="A110" s="35">
         <v>141</v>
       </c>
@@ -8845,7 +8769,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="111" ht="100.8">
+    <row r="111" ht="120">
       <c r="A111" s="35">
         <v>142</v>
       </c>
@@ -8888,7 +8812,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="112" ht="100.8">
+    <row r="112" ht="120">
       <c r="A112" s="35">
         <v>143</v>
       </c>
@@ -8931,7 +8855,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="113" ht="100.8">
+    <row r="113" ht="120">
       <c r="A113" s="35">
         <v>144</v>
       </c>
@@ -8974,7 +8898,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="114" ht="100.8">
+    <row r="114" ht="120">
       <c r="A114" s="35">
         <v>145</v>
       </c>
@@ -9017,7 +8941,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="115" ht="100.8">
+    <row r="115" ht="120">
       <c r="A115" s="35">
         <v>146</v>
       </c>
@@ -9060,7 +8984,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" ht="115.2">
+    <row r="116" ht="150">
       <c r="A116" s="35">
         <v>152</v>
       </c>
@@ -9080,13 +9004,13 @@
         <v>66</v>
       </c>
       <c r="G116" s="37" t="s">
-        <v>67</v>
+        <v>263</v>
       </c>
       <c r="H116" s="37" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I116" s="42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J116" s="38" t="s">
         <v>70</v>
@@ -9123,7 +9047,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="117" ht="115.2">
+    <row r="117" ht="150">
       <c r="A117" s="35">
         <v>154</v>
       </c>
@@ -9134,16 +9058,16 @@
         <v>64</v>
       </c>
       <c r="D117" s="35" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E117" s="43" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F117" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G117" s="37" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="H117" s="37" t="s">
         <v>268</v>
@@ -9186,7 +9110,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="118" ht="115.2">
+    <row r="118" ht="150">
       <c r="A118" s="35">
         <v>155</v>
       </c>
@@ -9206,13 +9130,13 @@
         <v>66</v>
       </c>
       <c r="G118" s="37" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="H118" s="37" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I118" s="42" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J118" s="38" t="s">
         <v>70</v>
@@ -9249,7 +9173,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" ht="115.2">
+    <row r="119" ht="150">
       <c r="A119" s="35">
         <v>156</v>
       </c>
@@ -9260,16 +9184,16 @@
         <v>64</v>
       </c>
       <c r="D119" s="35" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E119" s="43" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F119" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G119" s="37" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H119" s="37" t="s">
         <v>277</v>
@@ -9312,7 +9236,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="120" ht="115.2">
+    <row r="120" ht="150">
       <c r="A120" s="35">
         <v>159</v>
       </c>
@@ -9332,7 +9256,7 @@
         <v>66</v>
       </c>
       <c r="G120" s="37" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="H120" s="37" t="s">
         <v>281</v>
@@ -9375,7 +9299,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="121" ht="115.2">
+    <row r="121" ht="150">
       <c r="A121" s="35">
         <v>160</v>
       </c>
@@ -9395,13 +9319,13 @@
         <v>66</v>
       </c>
       <c r="G121" s="37" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H121" s="37" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I121" s="42" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="J121" s="38" t="s">
         <v>70</v>
@@ -9438,7 +9362,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="122" ht="115.2">
+    <row r="122" ht="150">
       <c r="A122" s="35">
         <v>161</v>
       </c>
@@ -9449,22 +9373,22 @@
         <v>64</v>
       </c>
       <c r="D122" s="35" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E122" s="43" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F122" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G122" s="37" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="H122" s="37" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I122" s="42" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J122" s="38" t="s">
         <v>70</v>
@@ -9501,7 +9425,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="123" ht="115.2">
+    <row r="123" ht="150">
       <c r="A123" s="35">
         <v>162</v>
       </c>
@@ -9512,16 +9436,16 @@
         <v>64</v>
       </c>
       <c r="D123" s="35" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E123" s="43" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F123" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G123" s="37" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="H123" s="37" t="s">
         <v>294</v>
@@ -9564,7 +9488,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" ht="115.2">
+    <row r="124" ht="150">
       <c r="A124" s="35">
         <v>163</v>
       </c>
@@ -9584,13 +9508,13 @@
         <v>66</v>
       </c>
       <c r="G124" s="37" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H124" s="37" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I124" s="42" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J124" s="38" t="s">
         <v>70</v>
@@ -9627,7 +9551,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="125" ht="115.2">
+    <row r="125" ht="150">
       <c r="A125" s="35">
         <v>164</v>
       </c>
@@ -9638,22 +9562,22 @@
         <v>64</v>
       </c>
       <c r="D125" s="35" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E125" s="43" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F125" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G125" s="37" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H125" s="37" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I125" s="42" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J125" s="38" t="s">
         <v>70</v>
@@ -9690,7 +9614,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="126" ht="115.2">
+    <row r="126" ht="150">
       <c r="A126" s="35">
         <v>165</v>
       </c>
@@ -9701,16 +9625,16 @@
         <v>64</v>
       </c>
       <c r="D126" s="35" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E126" s="43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F126" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G126" s="37" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="H126" s="37" t="s">
         <v>307</v>
@@ -9753,7 +9677,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" ht="115.2">
+    <row r="127" ht="150">
       <c r="A127" s="35">
         <v>166</v>
       </c>
@@ -9773,13 +9697,13 @@
         <v>66</v>
       </c>
       <c r="G127" s="37" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H127" s="37" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I127" s="42" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J127" s="38" t="s">
         <v>70</v>
@@ -9816,7 +9740,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="128" ht="115.2">
+    <row r="128" ht="150">
       <c r="A128" s="35">
         <v>167</v>
       </c>
@@ -9827,22 +9751,22 @@
         <v>64</v>
       </c>
       <c r="D128" s="35" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E128" s="43" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F128" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G128" s="37" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="H128" s="37" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="I128" s="42" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J128" s="38" t="s">
         <v>70</v>
@@ -9879,7 +9803,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="129" ht="115.2">
+    <row r="129" ht="150">
       <c r="A129" s="35">
         <v>168</v>
       </c>
@@ -9890,16 +9814,16 @@
         <v>64</v>
       </c>
       <c r="D129" s="35" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E129" s="43" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F129" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G129" s="37" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="H129" s="37" t="s">
         <v>320</v>
@@ -9942,7 +9866,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="130" ht="115.2">
+    <row r="130" ht="150">
       <c r="A130" s="35">
         <v>169</v>
       </c>
@@ -9962,13 +9886,13 @@
         <v>66</v>
       </c>
       <c r="G130" s="37" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H130" s="37" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I130" s="42" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="J130" s="38" t="s">
         <v>70</v>
@@ -10005,7 +9929,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="131" ht="100.8">
+    <row r="131" ht="120">
       <c r="A131" s="35">
         <v>175</v>
       </c>
@@ -10016,10 +9940,10 @@
         <v>60</v>
       </c>
       <c r="D131" s="35" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E131" s="43" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F131" s="37"/>
       <c r="G131" s="37"/>
@@ -10048,7 +9972,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="132" ht="100.8">
+    <row r="132" ht="120">
       <c r="A132" s="35">
         <v>177</v>
       </c>
@@ -10059,10 +9983,10 @@
         <v>60</v>
       </c>
       <c r="D132" s="35" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E132" s="43" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F132" s="37"/>
       <c r="G132" s="37"/>
@@ -10091,7 +10015,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="133" ht="100.8">
+    <row r="133" ht="120">
       <c r="A133" s="35">
         <v>178</v>
       </c>
@@ -10102,10 +10026,10 @@
         <v>60</v>
       </c>
       <c r="D133" s="35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E133" s="43" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F133" s="37"/>
       <c r="G133" s="37"/>
@@ -10134,7 +10058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="134" ht="100.8">
+    <row r="134" ht="120">
       <c r="A134" s="35">
         <v>179</v>
       </c>
@@ -10145,10 +10069,10 @@
         <v>60</v>
       </c>
       <c r="D134" s="35" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E134" s="43" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F134" s="37"/>
       <c r="G134" s="37"/>
@@ -10177,7 +10101,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" ht="100.8">
+    <row r="135" ht="120">
       <c r="A135" s="35">
         <v>180</v>
       </c>
@@ -10188,10 +10112,10 @@
         <v>60</v>
       </c>
       <c r="D135" s="35" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E135" s="43" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F135" s="37"/>
       <c r="G135" s="37"/>
@@ -10220,7 +10144,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="136" ht="100.8">
+    <row r="136" ht="120">
       <c r="A136" s="35">
         <v>181</v>
       </c>
@@ -10231,10 +10155,10 @@
         <v>60</v>
       </c>
       <c r="D136" s="35" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="E136" s="43" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F136" s="37"/>
       <c r="G136" s="37"/>
@@ -10263,7 +10187,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="137" ht="100.8">
+    <row r="137" ht="120">
       <c r="A137" s="35">
         <v>182</v>
       </c>
@@ -10274,10 +10198,10 @@
         <v>60</v>
       </c>
       <c r="D137" s="35" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E137" s="43" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F137" s="37"/>
       <c r="G137" s="37"/>
@@ -10306,7 +10230,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="138" ht="100.8">
+    <row r="138" ht="120">
       <c r="A138" s="35">
         <v>183</v>
       </c>
@@ -10317,10 +10241,10 @@
         <v>60</v>
       </c>
       <c r="D138" s="35" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E138" s="43" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F138" s="37"/>
       <c r="G138" s="37"/>
@@ -10349,7 +10273,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="139" ht="100.8">
+    <row r="139" ht="120">
       <c r="A139" s="35">
         <v>184</v>
       </c>
@@ -10360,10 +10284,10 @@
         <v>60</v>
       </c>
       <c r="D139" s="35" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E139" s="43" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F139" s="37"/>
       <c r="G139" s="37"/>
@@ -10392,7 +10316,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="140" ht="100.8">
+    <row r="140" ht="120">
       <c r="A140" s="35">
         <v>185</v>
       </c>
@@ -10403,10 +10327,10 @@
         <v>60</v>
       </c>
       <c r="D140" s="35" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E140" s="43" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F140" s="37"/>
       <c r="G140" s="37"/>
@@ -10435,7 +10359,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="141" ht="100.8">
+    <row r="141" ht="120">
       <c r="A141" s="35">
         <v>186</v>
       </c>
@@ -10446,10 +10370,10 @@
         <v>60</v>
       </c>
       <c r="D141" s="35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E141" s="43" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F141" s="37"/>
       <c r="G141" s="37"/>
@@ -10478,7 +10402,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="142" ht="100.8">
+    <row r="142" ht="120">
       <c r="A142" s="35">
         <v>187</v>
       </c>
@@ -10489,10 +10413,10 @@
         <v>60</v>
       </c>
       <c r="D142" s="35" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E142" s="43" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F142" s="37"/>
       <c r="G142" s="37"/>
@@ -10521,7 +10445,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="143" ht="100.8">
+    <row r="143" ht="120">
       <c r="A143" s="35">
         <v>188</v>
       </c>
@@ -10532,10 +10456,10 @@
         <v>60</v>
       </c>
       <c r="D143" s="35" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E143" s="43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F143" s="37"/>
       <c r="G143" s="37"/>
@@ -10564,7 +10488,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="144" ht="100.8">
+    <row r="144" ht="120">
       <c r="A144" s="35">
         <v>189</v>
       </c>
@@ -10575,10 +10499,10 @@
         <v>60</v>
       </c>
       <c r="D144" s="35" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E144" s="43" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="F144" s="37"/>
       <c r="G144" s="37"/>
@@ -10607,7 +10531,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="145" ht="100.8">
+    <row r="145" ht="120">
       <c r="A145" s="35">
         <v>190</v>
       </c>
@@ -10618,10 +10542,10 @@
         <v>60</v>
       </c>
       <c r="D145" s="35" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E145" s="43" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F145" s="37"/>
       <c r="G145" s="37"/>
@@ -10650,7 +10574,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="146" ht="129.6">
+    <row r="146" ht="135">
       <c r="A146" s="35">
         <v>191</v>
       </c>
@@ -10661,10 +10585,10 @@
         <v>48</v>
       </c>
       <c r="D146" s="35" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E146" s="43" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F146" s="37"/>
       <c r="G146" s="37"/>
@@ -10693,7 +10617,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="147" ht="129.6">
+    <row r="147" ht="150">
       <c r="A147" s="35">
         <v>376</v>
       </c>
@@ -10704,10 +10628,10 @@
         <v>48</v>
       </c>
       <c r="D147" s="35" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E147" s="43" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F147" s="37"/>
       <c r="G147" s="37"/>
@@ -10736,7 +10660,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="148" ht="115.2">
+    <row r="148" ht="135">
       <c r="A148" s="35">
         <v>417</v>
       </c>
@@ -10744,31 +10668,27 @@
         <v>47</v>
       </c>
       <c r="C148" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D148" s="35" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E148" s="43" t="s">
-        <v>362</v>
-      </c>
-      <c r="F148" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G148" s="37" t="s">
         <v>363</v>
       </c>
-      <c r="H148" s="37" t="s">
-        <v>364</v>
-      </c>
-      <c r="I148" s="42" t="s">
-        <v>365</v>
-      </c>
+      <c r="F148" s="37"/>
+      <c r="G148" s="37"/>
+      <c r="H148" s="37"/>
+      <c r="I148" s="42"/>
       <c r="J148" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K148" s="38"/>
-      <c r="L148" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K148" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L148" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M148" s="38"/>
       <c r="N148" s="38"/>
       <c r="O148" s="38"/>
@@ -10783,7 +10703,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="149" ht="129.6">
+    <row r="149" ht="150">
       <c r="A149" s="35">
         <v>418</v>
       </c>
@@ -10791,31 +10711,27 @@
         <v>47</v>
       </c>
       <c r="C149" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D149" s="35" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E149" s="43" t="s">
-        <v>367</v>
-      </c>
-      <c r="F149" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G149" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="H149" s="37" t="s">
-        <v>369</v>
-      </c>
-      <c r="I149" s="42" t="s">
-        <v>370</v>
-      </c>
+        <v>365</v>
+      </c>
+      <c r="F149" s="37"/>
+      <c r="G149" s="37"/>
+      <c r="H149" s="37"/>
+      <c r="I149" s="42"/>
       <c r="J149" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K149" s="38"/>
-      <c r="L149" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K149" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L149" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M149" s="38"/>
       <c r="N149" s="38"/>
       <c r="O149" s="38"/>
@@ -10830,7 +10746,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="150" ht="129.6">
+    <row r="150" ht="150">
       <c r="A150" s="35">
         <v>419</v>
       </c>
@@ -10838,13 +10754,13 @@
         <v>47</v>
       </c>
       <c r="C150" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D150" s="35" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E150" s="43" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="F150" s="37"/>
       <c r="G150" s="37"/>
@@ -10873,7 +10789,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="151" ht="144">
+    <row r="151" ht="150">
       <c r="A151" s="35">
         <v>423</v>
       </c>
@@ -10881,10 +10797,10 @@
         <v>47</v>
       </c>
       <c r="C151" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D151" s="35" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="E151" s="43" t="s">
         <v>56</v>
@@ -10916,7 +10832,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="152" ht="144">
+    <row r="152" ht="165">
       <c r="A152" s="35">
         <v>424</v>
       </c>
@@ -10924,10 +10840,10 @@
         <v>47</v>
       </c>
       <c r="C152" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D152" s="35" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E152" s="43" t="s">
         <v>80</v>
@@ -10959,7 +10875,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="153" ht="115.2">
+    <row r="153" ht="150">
       <c r="A153" s="35">
         <v>425</v>
       </c>
@@ -10967,13 +10883,13 @@
         <v>47</v>
       </c>
       <c r="C153" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D153" s="35" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E153" s="43" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="F153" s="37"/>
       <c r="G153" s="37"/>
@@ -11016,7 +10932,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="154" ht="115.2">
+    <row r="154" ht="135">
       <c r="A154" s="35">
         <v>432</v>
       </c>
@@ -11024,13 +10940,13 @@
         <v>47</v>
       </c>
       <c r="C154" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D154" s="35" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="E154" s="43" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="F154" s="37"/>
       <c r="G154" s="37"/>
@@ -11059,7 +10975,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="155" ht="115.2">
+    <row r="155" ht="135">
       <c r="A155" s="35">
         <v>433</v>
       </c>
@@ -11067,13 +10983,13 @@
         <v>47</v>
       </c>
       <c r="C155" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D155" s="35" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="E155" s="43" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="F155" s="37"/>
       <c r="G155" s="37"/>
@@ -11102,7 +11018,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="156" ht="115.2">
+    <row r="156" ht="135">
       <c r="A156" s="35">
         <v>434</v>
       </c>
@@ -11110,13 +11026,13 @@
         <v>47</v>
       </c>
       <c r="C156" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D156" s="35" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="E156" s="43" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="F156" s="37"/>
       <c r="G156" s="37"/>
@@ -11145,7 +11061,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="157" ht="115.2">
+    <row r="157" ht="135">
       <c r="A157" s="35">
         <v>435</v>
       </c>
@@ -11153,13 +11069,13 @@
         <v>47</v>
       </c>
       <c r="C157" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D157" s="35" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="E157" s="43" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="F157" s="37"/>
       <c r="G157" s="37"/>
@@ -11188,7 +11104,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="158" ht="115.2">
+    <row r="158" ht="135">
       <c r="A158" s="35">
         <v>437</v>
       </c>
@@ -11196,13 +11112,13 @@
         <v>47</v>
       </c>
       <c r="C158" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D158" s="35" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E158" s="43" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="F158" s="37"/>
       <c r="G158" s="37"/>
@@ -11231,7 +11147,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="159" ht="115.2">
+    <row r="159" ht="135">
       <c r="A159" s="35">
         <v>438</v>
       </c>
@@ -11239,13 +11155,13 @@
         <v>47</v>
       </c>
       <c r="C159" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D159" s="35" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E159" s="43" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="F159" s="37"/>
       <c r="G159" s="37"/>
@@ -11274,7 +11190,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="160" ht="115.2">
+    <row r="160" ht="135">
       <c r="A160" s="35">
         <v>440</v>
       </c>
@@ -11282,13 +11198,13 @@
         <v>47</v>
       </c>
       <c r="C160" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D160" s="35" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E160" s="43" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F160" s="37"/>
       <c r="G160" s="37"/>
@@ -11317,7 +11233,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="161" ht="115.2">
+    <row r="161" ht="135">
       <c r="A161" s="35">
         <v>441</v>
       </c>
@@ -11325,13 +11241,13 @@
         <v>47</v>
       </c>
       <c r="C161" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D161" s="35" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E161" s="43" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="F161" s="37"/>
       <c r="G161" s="37"/>
@@ -11360,7 +11276,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="162" ht="115.2">
+    <row r="162" ht="135">
       <c r="A162" s="35">
         <v>442</v>
       </c>
@@ -11368,13 +11284,13 @@
         <v>47</v>
       </c>
       <c r="C162" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D162" s="35" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E162" s="43" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="F162" s="37"/>
       <c r="G162" s="37"/>
@@ -11403,7 +11319,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="163" ht="115.2">
+    <row r="163" ht="135">
       <c r="A163" s="35">
         <v>443</v>
       </c>
@@ -11411,13 +11327,13 @@
         <v>47</v>
       </c>
       <c r="C163" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D163" s="35" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E163" s="43" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="F163" s="37"/>
       <c r="G163" s="37"/>
@@ -11446,7 +11362,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="164" ht="129.6">
+    <row r="164" ht="135">
       <c r="A164" s="35">
         <v>448</v>
       </c>
@@ -11457,22 +11373,22 @@
         <v>64</v>
       </c>
       <c r="D164" s="35" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="E164" s="43" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="F164" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G164" s="37" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="H164" s="37" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="I164" s="42" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="J164" s="38" t="s">
         <v>70</v>
@@ -11493,7 +11409,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="165" ht="129.6">
+    <row r="165" ht="135">
       <c r="A165" s="35">
         <v>449</v>
       </c>
@@ -11504,22 +11420,22 @@
         <v>64</v>
       </c>
       <c r="D165" s="35" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="E165" s="43" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="F165" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G165" s="37" t="s">
-        <v>403</v>
+        <v>324</v>
       </c>
       <c r="H165" s="37" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="I165" s="42" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="J165" s="38" t="s">
         <v>70</v>
@@ -11540,7 +11456,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="166" ht="115.2">
+    <row r="166" ht="135">
       <c r="A166" s="35">
         <v>450</v>
       </c>
@@ -11551,28 +11467,24 @@
         <v>58</v>
       </c>
       <c r="D166" s="35" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="E166" s="43" t="s">
-        <v>407</v>
-      </c>
-      <c r="F166" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G166" s="37" t="s">
-        <v>408</v>
-      </c>
-      <c r="H166" s="37" t="s">
-        <v>409</v>
-      </c>
-      <c r="I166" s="42" t="s">
-        <v>410</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="F166" s="37"/>
+      <c r="G166" s="37"/>
+      <c r="H166" s="37"/>
+      <c r="I166" s="42"/>
       <c r="J166" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K166" s="38"/>
-      <c r="L166" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K166" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L166" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M166" s="38"/>
       <c r="N166" s="38"/>
       <c r="O166" s="38"/>
@@ -11587,7 +11499,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="167" hidden="1" ht="115.2">
+    <row r="167" ht="135">
       <c r="A167" s="35">
         <v>451</v>
       </c>
@@ -11598,10 +11510,10 @@
         <v>58</v>
       </c>
       <c r="D167" s="35" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E167" s="43" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F167" s="37"/>
       <c r="G167" s="37"/>
@@ -11630,7 +11542,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="168" ht="129.6">
+    <row r="168" ht="150">
       <c r="A168" s="35">
         <v>452</v>
       </c>
@@ -11641,28 +11553,24 @@
         <v>48</v>
       </c>
       <c r="D168" s="35" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="E168" s="43" t="s">
-        <v>414</v>
-      </c>
-      <c r="F168" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G168" s="37" t="s">
-        <v>415</v>
-      </c>
-      <c r="H168" s="37" t="s">
-        <v>416</v>
-      </c>
-      <c r="I168" s="42" t="s">
-        <v>417</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="F168" s="37"/>
+      <c r="G168" s="37"/>
+      <c r="H168" s="37"/>
+      <c r="I168" s="42"/>
       <c r="J168" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K168" s="38"/>
-      <c r="L168" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K168" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L168" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M168" s="38"/>
       <c r="N168" s="38"/>
       <c r="O168" s="38"/>
@@ -11677,7 +11585,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="169" ht="115.2">
+    <row r="169" ht="135">
       <c r="A169" s="35">
         <v>454</v>
       </c>
@@ -11688,28 +11596,24 @@
         <v>77</v>
       </c>
       <c r="D169" s="35" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="E169" s="43" t="s">
-        <v>419</v>
-      </c>
-      <c r="F169" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G169" s="37" t="s">
-        <v>408</v>
-      </c>
-      <c r="H169" s="37" t="s">
-        <v>420</v>
-      </c>
-      <c r="I169" s="42" t="s">
-        <v>421</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="F169" s="37"/>
+      <c r="G169" s="37"/>
+      <c r="H169" s="37"/>
+      <c r="I169" s="42"/>
       <c r="J169" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K169" s="38"/>
-      <c r="L169" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K169" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L169" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M169" s="38"/>
       <c r="N169" s="38"/>
       <c r="O169" s="38"/>
@@ -11724,7 +11628,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="170" ht="115.2">
+    <row r="170" ht="135">
       <c r="A170" s="35">
         <v>455</v>
       </c>
@@ -11735,10 +11639,10 @@
         <v>77</v>
       </c>
       <c r="D170" s="35" t="s">
-        <v>422</v>
+        <v>408</v>
       </c>
       <c r="E170" s="43" t="s">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="F170" s="37"/>
       <c r="G170" s="37"/>
@@ -11767,7 +11671,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="171" ht="115.2">
+    <row r="171" ht="135">
       <c r="A171" s="35">
         <v>456</v>
       </c>
@@ -11778,28 +11682,24 @@
         <v>75</v>
       </c>
       <c r="D171" s="35" t="s">
-        <v>424</v>
+        <v>410</v>
       </c>
       <c r="E171" s="43" t="s">
-        <v>425</v>
-      </c>
-      <c r="F171" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G171" s="37" t="s">
-        <v>415</v>
-      </c>
-      <c r="H171" s="37" t="s">
-        <v>426</v>
-      </c>
-      <c r="I171" s="42" t="s">
-        <v>427</v>
-      </c>
+        <v>411</v>
+      </c>
+      <c r="F171" s="37"/>
+      <c r="G171" s="37"/>
+      <c r="H171" s="37"/>
+      <c r="I171" s="42"/>
       <c r="J171" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K171" s="38"/>
-      <c r="L171" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K171" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L171" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M171" s="38"/>
       <c r="N171" s="38"/>
       <c r="O171" s="38"/>
@@ -11814,7 +11714,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="172" ht="115.2">
+    <row r="172" ht="135">
       <c r="A172" s="35">
         <v>457</v>
       </c>
@@ -11825,28 +11725,24 @@
         <v>75</v>
       </c>
       <c r="D172" s="35" t="s">
-        <v>428</v>
+        <v>412</v>
       </c>
       <c r="E172" s="43" t="s">
-        <v>429</v>
-      </c>
-      <c r="F172" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G172" s="37" t="s">
-        <v>415</v>
-      </c>
-      <c r="H172" s="37" t="s">
-        <v>430</v>
-      </c>
-      <c r="I172" s="42" t="s">
-        <v>431</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="F172" s="37"/>
+      <c r="G172" s="37"/>
+      <c r="H172" s="37"/>
+      <c r="I172" s="42"/>
       <c r="J172" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K172" s="38"/>
-      <c r="L172" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K172" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L172" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M172" s="38"/>
       <c r="N172" s="38"/>
       <c r="O172" s="38"/>
@@ -11861,7 +11757,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="173" ht="115.2">
+    <row r="173" ht="135">
       <c r="A173" s="35">
         <v>458</v>
       </c>
@@ -11872,28 +11768,24 @@
         <v>73</v>
       </c>
       <c r="D173" s="35" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="E173" s="43" t="s">
-        <v>433</v>
-      </c>
-      <c r="F173" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G173" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="H173" s="37" t="s">
-        <v>435</v>
-      </c>
-      <c r="I173" s="42" t="s">
-        <v>436</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="F173" s="37"/>
+      <c r="G173" s="37"/>
+      <c r="H173" s="37"/>
+      <c r="I173" s="42"/>
       <c r="J173" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K173" s="38"/>
-      <c r="L173" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K173" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L173" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M173" s="38"/>
       <c r="N173" s="38"/>
       <c r="O173" s="38"/>
@@ -11908,7 +11800,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="174" ht="115.2">
+    <row r="174" ht="135">
       <c r="A174" s="35">
         <v>459</v>
       </c>
@@ -11919,10 +11811,10 @@
         <v>73</v>
       </c>
       <c r="D174" s="35" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
       <c r="E174" s="43" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="F174" s="37"/>
       <c r="G174" s="37"/>
@@ -11951,7 +11843,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="175" ht="115.2">
+    <row r="175" ht="135">
       <c r="A175" s="35">
         <v>460</v>
       </c>
@@ -11959,31 +11851,27 @@
         <v>47</v>
       </c>
       <c r="C175" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D175" s="35" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="E175" s="43" t="s">
-        <v>440</v>
-      </c>
-      <c r="F175" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G175" s="37" t="s">
-        <v>368</v>
-      </c>
-      <c r="H175" s="37" t="s">
-        <v>441</v>
-      </c>
-      <c r="I175" s="42" t="s">
-        <v>442</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="F175" s="37"/>
+      <c r="G175" s="37"/>
+      <c r="H175" s="37"/>
+      <c r="I175" s="42"/>
       <c r="J175" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K175" s="38"/>
-      <c r="L175" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K175" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L175" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M175" s="38"/>
       <c r="N175" s="38"/>
       <c r="O175" s="38"/>
@@ -11998,7 +11886,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="176" ht="100.8">
+    <row r="176" ht="120">
       <c r="A176" s="35">
         <v>461</v>
       </c>
@@ -12009,22 +11897,22 @@
         <v>64</v>
       </c>
       <c r="D176" s="35" t="s">
-        <v>443</v>
+        <v>420</v>
       </c>
       <c r="E176" s="43" t="s">
-        <v>444</v>
+        <v>421</v>
       </c>
       <c r="F176" s="35" t="s">
         <v>66</v>
       </c>
       <c r="G176" s="35" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="H176" s="35" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="I176" s="35" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="J176" s="38" t="s">
         <v>70</v>
@@ -12061,7 +11949,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="177" hidden="1" ht="115.2">
+    <row r="177" ht="120">
       <c r="A177" s="35">
         <v>462</v>
       </c>
@@ -12072,10 +11960,10 @@
         <v>62</v>
       </c>
       <c r="D177" s="35" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="E177" s="43" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="F177" s="35"/>
       <c r="G177" s="35"/>
@@ -12104,7 +11992,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="178" hidden="1" ht="100.8">
+    <row r="178" ht="120">
       <c r="A178" s="35">
         <v>463</v>
       </c>
@@ -12115,10 +12003,10 @@
         <v>77</v>
       </c>
       <c r="D178" s="35" t="s">
-        <v>449</v>
+        <v>427</v>
       </c>
       <c r="E178" s="43" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="F178" s="35"/>
       <c r="G178" s="35"/>
@@ -12147,7 +12035,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="179" hidden="1" ht="115.2">
+    <row r="179" ht="120">
       <c r="A179" s="35">
         <v>464</v>
       </c>
@@ -12158,10 +12046,10 @@
         <v>73</v>
       </c>
       <c r="D179" s="35" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="E179" s="43" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="F179" s="35"/>
       <c r="G179" s="35"/>
@@ -12190,7 +12078,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="180" hidden="1" ht="100.8">
+    <row r="180" ht="105">
       <c r="A180" s="35">
         <v>465</v>
       </c>
@@ -12201,10 +12089,10 @@
         <v>75</v>
       </c>
       <c r="D180" s="35" t="s">
-        <v>453</v>
+        <v>431</v>
       </c>
       <c r="E180" s="43" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="F180" s="35"/>
       <c r="G180" s="35"/>
@@ -12233,7 +12121,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="181" hidden="1" ht="100.8">
+    <row r="181" ht="105">
       <c r="A181" s="35">
         <v>466</v>
       </c>
@@ -12244,10 +12132,10 @@
         <v>48</v>
       </c>
       <c r="D181" s="35" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="E181" s="44" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="F181" s="35"/>
       <c r="G181" s="35"/>
@@ -12276,7 +12164,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="182" hidden="1" ht="100.8">
+    <row r="182" ht="105">
       <c r="A182" s="35">
         <v>467</v>
       </c>
@@ -12287,10 +12175,10 @@
         <v>58</v>
       </c>
       <c r="D182" s="35" t="s">
-        <v>457</v>
+        <v>435</v>
       </c>
       <c r="E182" s="43" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="F182" s="35"/>
       <c r="G182" s="35"/>
@@ -12319,7 +12207,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="183" ht="100.8">
+    <row r="183" ht="120">
       <c r="A183" s="35">
         <v>468</v>
       </c>
@@ -12330,22 +12218,22 @@
         <v>64</v>
       </c>
       <c r="D183" s="35" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="E183" s="43" t="s">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="F183" s="35" t="s">
         <v>66</v>
       </c>
       <c r="G183" s="35" t="s">
-        <v>403</v>
+        <v>422</v>
       </c>
       <c r="H183" s="35" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="I183" s="35" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="J183" s="38" t="s">
         <v>70</v>
@@ -12382,7 +12270,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="184" hidden="1" ht="100.8">
+    <row r="184" ht="120">
       <c r="A184" s="35">
         <v>469</v>
       </c>
@@ -12393,10 +12281,10 @@
         <v>60</v>
       </c>
       <c r="D184" s="35" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="E184" s="43" t="s">
-        <v>464</v>
+        <v>442</v>
       </c>
       <c r="F184" s="35"/>
       <c r="G184" s="35"/>
@@ -12425,7 +12313,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="185" hidden="1" ht="115.2">
+    <row r="185" ht="135">
       <c r="A185" s="35">
         <v>470</v>
       </c>
@@ -12433,13 +12321,13 @@
         <v>47</v>
       </c>
       <c r="C185" s="41" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D185" s="35" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="E185" s="43" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="F185" s="35"/>
       <c r="G185" s="35"/>
@@ -12468,7 +12356,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="186" ht="115.2">
+    <row r="186" ht="120">
       <c r="A186" s="35">
         <v>471</v>
       </c>
@@ -12479,28 +12367,24 @@
         <v>62</v>
       </c>
       <c r="D186" s="35" t="s">
-        <v>467</v>
+        <v>445</v>
       </c>
       <c r="E186" s="43" t="s">
-        <v>468</v>
-      </c>
-      <c r="F186" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="G186" s="37" t="s">
-        <v>434</v>
-      </c>
-      <c r="H186" s="37" t="s">
-        <v>469</v>
-      </c>
-      <c r="I186" s="42" t="s">
-        <v>470</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="F186" s="37"/>
+      <c r="G186" s="37"/>
+      <c r="H186" s="37"/>
+      <c r="I186" s="42"/>
       <c r="J186" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="K186" s="38"/>
-      <c r="L186" s="38"/>
+        <v>51</v>
+      </c>
+      <c r="K186" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="L186" s="38" t="s">
+        <v>53</v>
+      </c>
       <c r="M186" s="38"/>
       <c r="N186" s="38"/>
       <c r="O186" s="38"/>
@@ -12515,7 +12399,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="187" hidden="1" ht="115.2">
+    <row r="187" ht="120">
       <c r="A187" s="35">
         <v>472</v>
       </c>
@@ -12526,10 +12410,10 @@
         <v>62</v>
       </c>
       <c r="D187" s="35" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="E187" s="43" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="F187" s="37"/>
       <c r="G187" s="37"/>
@@ -12558,7 +12442,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="188" hidden="1" ht="115.2">
+    <row r="188" ht="120">
       <c r="A188" s="35">
         <v>473</v>
       </c>
@@ -12569,10 +12453,10 @@
         <v>48</v>
       </c>
       <c r="D188" s="41" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="E188" s="43" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="F188" s="37"/>
       <c r="G188" s="37"/>
@@ -12601,7 +12485,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="189" hidden="1" ht="100.8">
+    <row r="189" ht="105">
       <c r="A189" s="35">
         <v>474</v>
       </c>
@@ -12612,10 +12496,10 @@
         <v>62</v>
       </c>
       <c r="D189" s="35" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="E189" s="43" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="F189" s="37"/>
       <c r="G189" s="37"/>
@@ -12644,7 +12528,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="190" ht="115.2">
+    <row r="190" ht="150">
       <c r="A190" s="35">
         <v>475</v>
       </c>
@@ -12655,22 +12539,22 @@
         <v>64</v>
       </c>
       <c r="D190" s="35" t="s">
-        <v>477</v>
+        <v>453</v>
       </c>
       <c r="E190" s="43" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="F190" s="37" t="s">
         <v>66</v>
       </c>
       <c r="G190" s="37" t="s">
-        <v>479</v>
+        <v>422</v>
       </c>
       <c r="H190" s="37" t="s">
-        <v>480</v>
+        <v>455</v>
       </c>
       <c r="I190" s="42" t="s">
-        <v>481</v>
+        <v>456</v>
       </c>
       <c r="J190" s="38" t="s">
         <v>70</v>
@@ -12707,7 +12591,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="191" hidden="1" ht="129.6">
+    <row r="191" ht="150">
       <c r="A191" s="35">
         <v>476</v>
       </c>
@@ -12718,10 +12602,10 @@
         <v>60</v>
       </c>
       <c r="D191" s="35" t="s">
-        <v>482</v>
+        <v>457</v>
       </c>
       <c r="E191" s="43" t="s">
-        <v>483</v>
+        <v>458</v>
       </c>
       <c r="F191" s="37"/>
       <c r="G191" s="37"/>
@@ -12750,7 +12634,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="192" hidden="1" ht="129.6">
+    <row r="192" ht="150">
       <c r="A192" s="35">
         <v>477</v>
       </c>
@@ -12761,10 +12645,10 @@
         <v>60</v>
       </c>
       <c r="D192" s="35" t="s">
-        <v>484</v>
+        <v>459</v>
       </c>
       <c r="E192" s="43" t="s">
-        <v>485</v>
+        <v>460</v>
       </c>
       <c r="F192" s="37"/>
       <c r="G192" s="37"/>
@@ -12793,7 +12677,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="193" hidden="1" ht="100.8">
+    <row r="193" ht="105">
       <c r="A193" s="35">
         <v>478</v>
       </c>
@@ -12804,10 +12688,10 @@
         <v>60</v>
       </c>
       <c r="D193" s="35" t="s">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="E193" s="45" t="s">
-        <v>487</v>
+        <v>462</v>
       </c>
       <c r="F193" s="37"/>
       <c r="G193" s="37"/>
@@ -16788,13 +16672,7 @@
       <c r="W745" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="SI"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A9:W193" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -16808,7 +16686,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -16816,7 +16694,7 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M154:N193 J10:J193 M35:N152 P154:R193 P35:R152 M10:N26 P10:R26</xm:sqref>
+          <xm:sqref>M154:N193 P10:R26 M35:N152 P154:R193 P35:R152 M10:N26 J10:J193</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
@@ -16839,41 +16717,41 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09A7248B-FC5F-481F-A206-5035B67EFB69}">
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>488</v>
+        <v>463</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>491</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>494</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -16890,35 +16768,35 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1" style="16"/>
-    <col min="2" max="2" width="23.88671875" customWidth="1"/>
-    <col min="3" max="3" width="33.88671875" customWidth="1"/>
+    <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
     <col min="4" max="4" width="102" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" customWidth="1"/>
-    <col min="7" max="7" bestFit="1" width="7.88671875" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" customWidth="1"/>
+    <col min="7" max="7" bestFit="1" width="7.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>495</v>
+        <v>470</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="11" t="s">
-        <v>496</v>
+        <v>471</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>498</v>
+        <v>473</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>499</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" ht="14.25" customHeight="1">
@@ -16926,13 +16804,13 @@
         <v>48</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="D2" s="30" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" ht="14.25" customHeight="1">
@@ -16940,13 +16818,13 @@
         <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
       <c r="D3" s="30" t="s">
-        <v>504</v>
+        <v>479</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1">
@@ -16954,13 +16832,13 @@
         <v>62</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>505</v>
+        <v>480</v>
       </c>
       <c r="D4" s="31" t="s">
-        <v>506</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1">
@@ -16968,13 +16846,13 @@
         <v>73</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>507</v>
+        <v>482</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>508</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" ht="14.25" customHeight="1">
@@ -16982,83 +16860,83 @@
         <v>75</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>509</v>
+        <v>484</v>
       </c>
       <c r="D6" s="31" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="7" ht="14.4">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>511</v>
+        <v>486</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="8" ht="14.4">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>513</v>
+        <v>488</v>
       </c>
       <c r="D8" s="31" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="9" ht="14.4">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>515</v>
+        <v>490</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="10" ht="43.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="10" ht="45">
       <c r="A10" s="5" t="s">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>518</v>
+        <v>493</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>519</v>
+        <v>494</v>
       </c>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>500</v>
+        <v>475</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>520</v>
+        <v>495</v>
       </c>
       <c r="D11" s="31" t="s">
-        <v>521</v>
+        <v>496</v>
       </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
@@ -18025,11 +17903,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="13.109375" customWidth="1"/>
-    <col min="3" max="6" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" customWidth="1"/>
+    <col min="3" max="6" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -18042,7 +17920,7 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>522</v>
+        <v>497</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>70</v>
@@ -18050,7 +17928,7 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>523</v>
+        <v>498</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>51</v>
@@ -19073,6 +18951,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE9A258ADBC3EC4CBEB1E2AB9909207A" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="0284f501378927579289f00316ec8a74">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="295b7897-c886-40bf-9750-5782b814c3e4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b47213d65be806e283915cff374a7eef" ns2:_="">
     <xsd:import namespace="295b7897-c886-40bf-9750-5782b814c3e4"/>
@@ -19216,22 +19109,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7568E770-0BC4-46AF-B6C6-958AE21C8F7F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -19249,31 +19152,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{e0793d39-0939-496d-b129-198edd916feb}" enabled="0" method="" siteId="{e0793d39-0939-496d-b129-198edd916feb}" removed="1"/>
